--- a/registration_forms/028_psa_form--registration_forms.xlsx
+++ b/registration_forms/028_psa_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Kid 1 First Name</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Kid 1 Last Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Date Of Birth</t>
+          <t>Kid 1 Date Of Birth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Kid 1 Age</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Kid 1 Contact Number</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Kid 1 Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Kid 1 Medical Conditions</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Kid 2 First Name</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Kid 2 Last Name</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date Of Birth</t>
+          <t>Kid 2 Date Of Birth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Kid 2 Age</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Kid 2 Contact Number</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Kid 3 First Name</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Kid 3 Last Name</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Date Of Birth</t>
+          <t>Kid 3 Date Of Birth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Kid 3 Age</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Kid 3 Contact Number</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Kid 4 First Name</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Kid 4 Last Name</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Date Of Birth</t>
+          <t>Kid 4 Date Of Birth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Kid 4 Age</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Kid 4 Contact Number</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Kid 5 First Name</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Kid 5 Last Name</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Date Of Birth</t>
+          <t>Kid 5 Date Of Birth</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Kid 5 Age</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Kid 5 Contact Number</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
